--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>92843</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>92843</v>
+        <v>92935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>92935</v>
+        <v>92947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>92947</v>
+        <v>92949</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>92949</v>
+        <v>92989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -768,7 +768,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>91592</v>
+        <v>91593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>91598</v>
+        <v>91602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 54044-2024 artfynd.xlsx
+++ b/artfynd/A 54044-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>128105040</v>
       </c>
       <c r="B2" t="n">
-        <v>91602</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,6 +769,1078 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119000821</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93189</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Petikån, Petikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>730581</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7217691</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119000778</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Petikån, Petikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>730597</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7217729</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119000799</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Petikån, Petikån, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>730573</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7217703</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>119022697</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hällbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>730591</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7217693</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>119022698</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hällbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>730588</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7217725</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119022702</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93191</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hällbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>730598</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7217751</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119022699</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hällbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>730597</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7217746</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119022701</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hällbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>730600</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7217748</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>119022680</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hällbäcken, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>730599</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7217731</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström, Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126596778</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Petikån, norr, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>730497</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7217488</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norsjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-11</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
         <is>
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
